--- a/table/Datas/#GameMode.xlsx
+++ b/table/Datas/#GameMode.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,6 +452,11 @@
           <t>max_players</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>scene_path</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -489,6 +494,11 @@
           <t>int</t>
         </is>
       </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -496,8 +506,6 @@
           <t>##group</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>c</t>
@@ -508,8 +516,11 @@
           <t>c</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>c,s</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -545,6 +556,11 @@
       <c r="G4" t="inlineStr">
         <is>
           <t>max_players</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>scene_path</t>
         </is>
       </c>
     </row>
@@ -562,12 +578,16 @@
           <t>플랩왕</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
         <v>2</v>
       </c>
       <c r="G5" t="n">
         <v>8</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Assets/Scenes/FlapWang.unity</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -584,7 +604,6 @@
           <t>닷지볼</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
         <v>2</v>
       </c>
@@ -606,7 +625,6 @@
           <t>관찰자 피하기</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
         <v>2</v>
       </c>
@@ -628,7 +646,6 @@
           <t>기억력 게임</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
         <v>2</v>
       </c>
@@ -650,7 +667,6 @@
           <t>타겟 슈팅</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
         <v>2</v>
       </c>

--- a/table/Datas/#GameMode.xlsx
+++ b/table/Datas/#GameMode.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,6 +674,43 @@
         <v>8</v>
       </c>
     </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FlappyRace</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>플래피 레이스</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>날개짓으로 코스를 통과해 결승선에 먼저 닿는 레이스</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Assets/Scenes/FlappyRace.unity</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/#GameMode.xlsx
+++ b/table/Datas/#GameMode.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H10"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,6 +711,37 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="B11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Panchigi</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>판치기</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>번갈아 쳐서 동전을 모두 뒤집는 사람이 이긴다</t>
+        </is>
+      </c>
+      <c r="F11" t="n">
+        <v>2</v>
+      </c>
+      <c r="G11" t="n">
+        <v>4</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Assets/Scenes/Panchigi.unity</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/#GameMode.xlsx
+++ b/table/Datas/#GameMode.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -742,6 +742,38 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr"/>
+      <c r="B12" t="n">
+        <v>8</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Skydive</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>스카이다이브</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>하늘에서 레이저를 피해 내려가는 레이스</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>2</v>
+      </c>
+      <c r="G12" t="n">
+        <v>8</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Assets/Scenes/Skydive.unity</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/table/Datas/#GameMode.xlsx
+++ b/table/Datas/#GameMode.xlsx
@@ -659,19 +659,29 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>TargetShooting</t>
+          <t>Archery</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>타겟 슈팅</t>
+          <t>활쏘기</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>함정을 가려내며 적은 과녁을 다투는 활쏘기</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
         <v>8</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Assets/Scenes/Archery.unity</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -743,7 +753,6 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr"/>
       <c r="B12" t="n">
         <v>8</v>
       </c>
